--- a/docs/downloads/13/tbl_repondant_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/13/tbl_repondant_marovoay_madiromiongana.xlsx
@@ -382,9 +382,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -397,9 +394,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -427,9 +421,6 @@
           <t>Code NA</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -472,9 +463,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -502,9 +490,6 @@
           <t>Code 10</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -516,9 +501,6 @@
         <is>
           <t>Code NA</t>
         </is>
-      </c>
-      <c r="C11">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
